--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 15M D100 QA Spring 2024 24GH00Q73 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 15M D100 QA Spring 2024 24GH00Q73 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Zooplankton Counts\Huron\Spring 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F92DF98-7395-4617-8F38-7088A71064B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918A5E85-689A-44C1-A0A4-9D81202B8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{DD104851-B488-4134-9780-3C7A00C6C097}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD104851-B488-4134-9780-3C7A00C6C097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="7" r:id="rId2"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -482,7 +481,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -498,6 +497,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -510,8 +510,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7825,7 +7823,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EA31020-97E3-491F-B525-88F51CF15462}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EA31020-97E3-491F-B525-88F51CF15462}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -8272,21 +8270,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0130CE54-2207-43E4-84B1-DEF2A2692AF2}">
   <dimension ref="A1:Y361"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.85546875" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" customWidth="1"/>
-    <col min="20" max="20" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.88671875" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" customWidth="1"/>
+    <col min="20" max="20" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8342,7 +8340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -8401,7 +8399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -8472,7 +8470,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -8527,19 +8525,17 @@
       <c r="T4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="15">
+      <c r="U4">
         <v>41</v>
       </c>
-      <c r="V4" s="15">
+      <c r="V4">
         <v>45</v>
       </c>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15">
+      <c r="Y4">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -8594,21 +8590,20 @@
       <c r="T5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U5" s="15">
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" s="15">
+      <c r="V5">
         <v>0</v>
       </c>
-      <c r="W5" s="15">
+      <c r="W5">
         <v>5</v>
       </c>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15">
+      <c r="Y5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -8663,19 +8658,17 @@
       <c r="T6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="U6" s="15">
+      <c r="U6">
         <v>42</v>
       </c>
-      <c r="V6" s="15">
+      <c r="V6">
         <v>41</v>
       </c>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="15">
+      <c r="Y6">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8730,19 +8723,17 @@
       <c r="T7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="15">
-        <v>24</v>
-      </c>
-      <c r="V7" s="15">
+      <c r="U7">
+        <v>24</v>
+      </c>
+      <c r="V7">
         <v>26</v>
       </c>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="15">
+      <c r="Y7">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -8797,19 +8788,17 @@
       <c r="T8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="U8" s="15">
+      <c r="U8">
         <v>80</v>
       </c>
-      <c r="V8" s="15">
+      <c r="V8">
         <v>87</v>
       </c>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15">
+      <c r="Y8">
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -8864,19 +8853,17 @@
       <c r="T9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="U9" s="15">
+      <c r="U9">
         <v>71</v>
       </c>
-      <c r="V9" s="15">
+      <c r="V9">
         <v>75</v>
       </c>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15">
+      <c r="Y9">
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -8931,19 +8918,17 @@
       <c r="T10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="U10" s="15">
+      <c r="U10">
         <v>52</v>
       </c>
-      <c r="V10" s="15">
+      <c r="V10">
         <v>53</v>
       </c>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15">
+      <c r="Y10">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -8998,21 +8983,20 @@
       <c r="T11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="U11" s="15">
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="V11" s="15">
+      <c r="V11">
         <v>0</v>
       </c>
-      <c r="W11" s="15">
+      <c r="W11">
         <v>0</v>
       </c>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15">
+      <c r="Y11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -9067,23 +9051,23 @@
       <c r="T12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U12" s="15">
+      <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" s="15">
+      <c r="V12">
         <v>3</v>
       </c>
-      <c r="W12" s="15">
+      <c r="W12">
         <v>5</v>
       </c>
-      <c r="X12" s="15">
+      <c r="X12">
         <v>1</v>
       </c>
-      <c r="Y12" s="15">
+      <c r="Y12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -9138,23 +9122,23 @@
       <c r="T13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="U13" s="15">
+      <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" s="15">
+      <c r="V13">
         <v>0</v>
       </c>
-      <c r="W13" s="15">
+      <c r="W13">
         <v>0</v>
       </c>
-      <c r="X13" s="15">
+      <c r="X13">
         <v>3</v>
       </c>
-      <c r="Y13" s="15">
+      <c r="Y13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -9209,21 +9193,20 @@
       <c r="T14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="U14" s="15">
+      <c r="U14">
         <v>1</v>
       </c>
-      <c r="V14" s="15">
+      <c r="V14">
         <v>2</v>
       </c>
-      <c r="W14" s="15">
+      <c r="W14">
         <v>1</v>
       </c>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="15">
+      <c r="Y14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -9278,21 +9261,20 @@
       <c r="T15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="U15" s="15">
+      <c r="U15">
         <v>5</v>
       </c>
-      <c r="V15" s="15">
+      <c r="V15">
         <v>11</v>
       </c>
-      <c r="W15" s="15">
-        <v>23</v>
-      </c>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15">
+      <c r="W15">
+        <v>23</v>
+      </c>
+      <c r="Y15">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -9347,21 +9329,20 @@
       <c r="T16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="U16" s="15">
+      <c r="U16">
         <v>1</v>
       </c>
-      <c r="V16" s="15">
+      <c r="V16">
         <v>1</v>
       </c>
-      <c r="W16" s="15">
+      <c r="W16">
         <v>0</v>
       </c>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15">
+      <c r="Y16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -9416,23 +9397,23 @@
       <c r="T17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="U17" s="15">
+      <c r="U17">
         <v>318</v>
       </c>
-      <c r="V17" s="15">
+      <c r="V17">
         <v>344</v>
       </c>
-      <c r="W17" s="15">
+      <c r="W17">
         <v>34</v>
       </c>
-      <c r="X17" s="15">
+      <c r="X17">
         <v>4</v>
       </c>
-      <c r="Y17" s="15">
+      <c r="Y17">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -9485,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -9537,17 +9518,17 @@
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="T19" s="12" t="s">
         <v>72</v>
       </c>
       <c r="U19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V19" s="16">
+      <c r="V19" s="11">
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -9599,15 +9580,15 @@
       <c r="Q20">
         <v>1</v>
       </c>
-      <c r="T20" s="12"/>
+      <c r="T20" s="13"/>
       <c r="U20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V20" s="16">
+      <c r="V20" s="11">
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -9659,17 +9640,17 @@
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="T21" s="12" t="s">
         <v>74</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V21" s="16">
+      <c r="V21" s="11">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -9721,15 +9702,15 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="T22" s="12"/>
+      <c r="T22" s="13"/>
       <c r="U22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V22" s="16">
+      <c r="V22" s="11">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -9784,12 +9765,12 @@
       <c r="T23" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="13" t="s">
+      <c r="U23" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="V23" s="14"/>
-    </row>
-    <row r="24" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V23" s="15"/>
+    </row>
+    <row r="24" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -9844,12 +9825,12 @@
       <c r="T24" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U24" s="13" t="s">
+      <c r="U24" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="V24" s="14"/>
-    </row>
-    <row r="25" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V24" s="15"/>
+    </row>
+    <row r="25" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -9904,10 +9885,10 @@
       <c r="T25" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="U25" s="13"/>
-      <c r="V25" s="14"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U25" s="14"/>
+      <c r="V25" s="15"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -9960,7 +9941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -10013,7 +9994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -10066,7 +10047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -10119,7 +10100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -10172,7 +10153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -10225,7 +10206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -10278,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -10331,7 +10312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -10384,7 +10365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -10437,7 +10418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -10490,7 +10471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -10543,7 +10524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -10596,7 +10577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -10649,7 +10630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -10702,7 +10683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>30</v>
       </c>
@@ -10755,7 +10736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>30</v>
       </c>
@@ -10808,7 +10789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -10861,7 +10842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -10914,7 +10895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -10967,7 +10948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -11020,7 +11001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>30</v>
       </c>
@@ -11073,7 +11054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -11126,7 +11107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -11179,7 +11160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -11232,7 +11213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>30</v>
       </c>
@@ -11285,7 +11266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -11338,7 +11319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>30</v>
       </c>
@@ -11391,7 +11372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>30</v>
       </c>
@@ -11444,7 +11425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -11497,7 +11478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>30</v>
       </c>
@@ -11550,7 +11531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>30</v>
       </c>
@@ -11603,7 +11584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>30</v>
       </c>
@@ -11656,7 +11637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>30</v>
       </c>
@@ -11709,7 +11690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>30</v>
       </c>
@@ -11762,7 +11743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
@@ -11815,7 +11796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>30</v>
       </c>
@@ -11868,7 +11849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>30</v>
       </c>
@@ -11921,7 +11902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>30</v>
       </c>
@@ -11974,7 +11955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -12027,7 +12008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -12080,7 +12061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -12133,7 +12114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -12186,7 +12167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -12239,7 +12220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -12292,7 +12273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -12345,7 +12326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>30</v>
       </c>
@@ -12398,7 +12379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>30</v>
       </c>
@@ -12451,7 +12432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>30</v>
       </c>
@@ -12504,7 +12485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>30</v>
       </c>
@@ -12557,7 +12538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>30</v>
       </c>
@@ -12610,7 +12591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>30</v>
       </c>
@@ -12663,7 +12644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>30</v>
       </c>
@@ -12716,7 +12697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -12769,7 +12750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -12822,7 +12803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -12875,7 +12856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -12928,7 +12909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -12981,7 +12962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -13034,7 +13015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -13087,7 +13068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>30</v>
       </c>
@@ -13140,7 +13121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -13193,7 +13174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -13246,7 +13227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -13299,7 +13280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -13352,7 +13333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -13405,7 +13386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -13458,7 +13439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -13511,7 +13492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -13564,7 +13545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -13617,7 +13598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -13670,7 +13651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -13723,7 +13704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -13779,7 +13760,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -13832,7 +13813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>30</v>
       </c>
@@ -13885,7 +13866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -13938,7 +13919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>30</v>
       </c>
@@ -13991,7 +13972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -14044,7 +14025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -14097,7 +14078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>30</v>
       </c>
@@ -14150,7 +14131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>30</v>
       </c>
@@ -14203,7 +14184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>30</v>
       </c>
@@ -14256,7 +14237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>30</v>
       </c>
@@ -14309,7 +14290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>30</v>
       </c>
@@ -14362,7 +14343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>30</v>
       </c>
@@ -14415,7 +14396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>30</v>
       </c>
@@ -14471,7 +14452,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -14524,7 +14505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>30</v>
       </c>
@@ -14577,7 +14558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>30</v>
       </c>
@@ -14630,7 +14611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>30</v>
       </c>
@@ -14683,7 +14664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>30</v>
       </c>
@@ -14736,7 +14717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>30</v>
       </c>
@@ -14789,7 +14770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>30</v>
       </c>
@@ -14842,7 +14823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>30</v>
       </c>
@@ -14895,7 +14876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -14948,7 +14929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -15001,7 +14982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -15054,7 +15035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -15107,7 +15088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -15160,7 +15141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>30</v>
       </c>
@@ -15213,7 +15194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>30</v>
       </c>
@@ -15266,7 +15247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>30</v>
       </c>
@@ -15319,7 +15300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -15372,7 +15353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -15425,7 +15406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -15478,7 +15459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>30</v>
       </c>
@@ -15531,7 +15512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>30</v>
       </c>
@@ -15584,7 +15565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>30</v>
       </c>
@@ -15637,7 +15618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>30</v>
       </c>
@@ -15690,7 +15671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>30</v>
       </c>
@@ -15743,7 +15724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>30</v>
       </c>
@@ -15796,7 +15777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>30</v>
       </c>
@@ -15849,7 +15830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>30</v>
       </c>
@@ -15902,7 +15883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>30</v>
       </c>
@@ -15955,7 +15936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>30</v>
       </c>
@@ -16008,7 +15989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>30</v>
       </c>
@@ -16061,7 +16042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>30</v>
       </c>
@@ -16114,7 +16095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>30</v>
       </c>
@@ -16167,7 +16148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>30</v>
       </c>
@@ -16220,7 +16201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>30</v>
       </c>
@@ -16273,7 +16254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>30</v>
       </c>
@@ -16326,7 +16307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>30</v>
       </c>
@@ -16379,7 +16360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>30</v>
       </c>
@@ -16432,7 +16413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>30</v>
       </c>
@@ -16485,7 +16466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>30</v>
       </c>
@@ -16538,7 +16519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>30</v>
       </c>
@@ -16591,7 +16572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>30</v>
       </c>
@@ -16644,7 +16625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>30</v>
       </c>
@@ -16697,7 +16678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>30</v>
       </c>
@@ -16750,7 +16731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>30</v>
       </c>
@@ -16803,7 +16784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>30</v>
       </c>
@@ -16856,7 +16837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>30</v>
       </c>
@@ -16909,7 +16890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>30</v>
       </c>
@@ -16962,7 +16943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>30</v>
       </c>
@@ -17015,7 +16996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -17068,7 +17049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>30</v>
       </c>
@@ -17121,7 +17102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>30</v>
       </c>
@@ -17174,7 +17155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>30</v>
       </c>
@@ -17227,7 +17208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>30</v>
       </c>
@@ -17280,7 +17261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>30</v>
       </c>
@@ -17333,7 +17314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>30</v>
       </c>
@@ -17386,7 +17367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>30</v>
       </c>
@@ -17439,7 +17420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>30</v>
       </c>
@@ -17495,7 +17476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>30</v>
       </c>
@@ -17548,7 +17529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>30</v>
       </c>
@@ -17601,7 +17582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>30</v>
       </c>
@@ -17654,7 +17635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>30</v>
       </c>
@@ -17707,7 +17688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>30</v>
       </c>
@@ -17760,7 +17741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>30</v>
       </c>
@@ -17813,7 +17794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>30</v>
       </c>
@@ -17866,7 +17847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>30</v>
       </c>
@@ -17919,7 +17900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>30</v>
       </c>
@@ -17957,10 +17938,10 @@
         <v>59</v>
       </c>
       <c r="M177" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N177" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="O177">
         <v>0.59899999999999998</v>
@@ -17972,7 +17953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>30</v>
       </c>
@@ -18025,7 +18006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>30</v>
       </c>
@@ -18078,7 +18059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>30</v>
       </c>
@@ -18131,7 +18112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>30</v>
       </c>
@@ -18184,7 +18165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>30</v>
       </c>
@@ -18237,7 +18218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>30</v>
       </c>
@@ -18290,7 +18271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>30</v>
       </c>
@@ -18343,7 +18324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>30</v>
       </c>
@@ -18396,7 +18377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>30</v>
       </c>
@@ -18449,7 +18430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>30</v>
       </c>
@@ -18502,7 +18483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>30</v>
       </c>
@@ -18555,7 +18536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>30</v>
       </c>
@@ -18608,7 +18589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>30</v>
       </c>
@@ -18661,7 +18642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>30</v>
       </c>
@@ -18714,7 +18695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>30</v>
       </c>
@@ -18767,7 +18748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>30</v>
       </c>
@@ -18820,7 +18801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>30</v>
       </c>
@@ -18873,7 +18854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>30</v>
       </c>
@@ -18926,7 +18907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>30</v>
       </c>
@@ -18979,7 +18960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>30</v>
       </c>
@@ -19032,7 +19013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>30</v>
       </c>
@@ -19085,7 +19066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>30</v>
       </c>
@@ -19138,7 +19119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>30</v>
       </c>
@@ -19191,7 +19172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>30</v>
       </c>
@@ -19244,7 +19225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>30</v>
       </c>
@@ -19297,7 +19278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>30</v>
       </c>
@@ -19350,7 +19331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>30</v>
       </c>
@@ -19403,7 +19384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>30</v>
       </c>
@@ -19456,7 +19437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>30</v>
       </c>
@@ -19509,7 +19490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>30</v>
       </c>
@@ -19562,7 +19543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>30</v>
       </c>
@@ -19615,7 +19596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>30</v>
       </c>
@@ -19668,7 +19649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>30</v>
       </c>
@@ -19721,7 +19702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>30</v>
       </c>
@@ -19774,7 +19755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>30</v>
       </c>
@@ -19827,7 +19808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>30</v>
       </c>
@@ -19880,7 +19861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>30</v>
       </c>
@@ -19933,7 +19914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>30</v>
       </c>
@@ -19986,7 +19967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>30</v>
       </c>
@@ -20039,7 +20020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>30</v>
       </c>
@@ -20092,7 +20073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>30</v>
       </c>
@@ -20145,7 +20126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>30</v>
       </c>
@@ -20198,7 +20179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>30</v>
       </c>
@@ -20251,7 +20232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>30</v>
       </c>
@@ -20304,7 +20285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>30</v>
       </c>
@@ -20357,7 +20338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>30</v>
       </c>
@@ -20410,7 +20391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>30</v>
       </c>
@@ -20463,7 +20444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>30</v>
       </c>
@@ -20516,7 +20497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>30</v>
       </c>
@@ -20569,7 +20550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>30</v>
       </c>
@@ -20622,7 +20603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>30</v>
       </c>
@@ -20675,7 +20656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>30</v>
       </c>
@@ -20728,7 +20709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>30</v>
       </c>
@@ -20781,7 +20762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>30</v>
       </c>
@@ -20834,7 +20815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>30</v>
       </c>
@@ -20887,7 +20868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>30</v>
       </c>
@@ -20940,7 +20921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>30</v>
       </c>
@@ -20993,7 +20974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>30</v>
       </c>
@@ -21046,7 +21027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>30</v>
       </c>
@@ -21099,7 +21080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>30</v>
       </c>
@@ -21152,7 +21133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>30</v>
       </c>
@@ -21205,7 +21186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>30</v>
       </c>
@@ -21258,7 +21239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -21311,7 +21292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>30</v>
       </c>
@@ -21364,7 +21345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>30</v>
       </c>
@@ -21417,7 +21398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>30</v>
       </c>
@@ -21470,7 +21451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>30</v>
       </c>
@@ -21523,7 +21504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>30</v>
       </c>
@@ -21576,7 +21557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>30</v>
       </c>
@@ -21629,7 +21610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>30</v>
       </c>
@@ -21682,7 +21663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>30</v>
       </c>
@@ -21735,7 +21716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>30</v>
       </c>
@@ -21788,7 +21769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>30</v>
       </c>
@@ -21841,7 +21822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>30</v>
       </c>
@@ -21894,7 +21875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>30</v>
       </c>
@@ -21947,7 +21928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>30</v>
       </c>
@@ -22000,7 +21981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>30</v>
       </c>
@@ -22053,7 +22034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>30</v>
       </c>
@@ -22106,7 +22087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>30</v>
       </c>
@@ -22159,7 +22140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>30</v>
       </c>
@@ -22212,7 +22193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>30</v>
       </c>
@@ -22265,7 +22246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -22318,7 +22299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>30</v>
       </c>
@@ -22371,7 +22352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>30</v>
       </c>
@@ -22424,7 +22405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>30</v>
       </c>
@@ -22477,7 +22458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>30</v>
       </c>
@@ -22530,7 +22511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>30</v>
       </c>
@@ -22583,7 +22564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>30</v>
       </c>
@@ -22636,7 +22617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>30</v>
       </c>
@@ -22689,7 +22670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>30</v>
       </c>
@@ -22742,7 +22723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>30</v>
       </c>
@@ -22795,7 +22776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>30</v>
       </c>
@@ -22848,7 +22829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>30</v>
       </c>
@@ -22901,7 +22882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>30</v>
       </c>
@@ -22954,7 +22935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>30</v>
       </c>
@@ -23007,7 +22988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>30</v>
       </c>
@@ -23060,7 +23041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>30</v>
       </c>
@@ -23113,7 +23094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>30</v>
       </c>
@@ -23166,7 +23147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>30</v>
       </c>
@@ -23219,7 +23200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>30</v>
       </c>
@@ -23272,7 +23253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>30</v>
       </c>
@@ -23325,7 +23306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>30</v>
       </c>
@@ -23378,7 +23359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>30</v>
       </c>
@@ -23431,7 +23412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>30</v>
       </c>
@@ -23484,7 +23465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>30</v>
       </c>
@@ -23537,7 +23518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>30</v>
       </c>
@@ -23590,7 +23571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>30</v>
       </c>
@@ -23643,7 +23624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>30</v>
       </c>
@@ -23696,7 +23677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>30</v>
       </c>
@@ -23749,7 +23730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>30</v>
       </c>
@@ -23802,7 +23783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>30</v>
       </c>
@@ -23855,7 +23836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>30</v>
       </c>
@@ -23908,7 +23889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>30</v>
       </c>
@@ -23961,7 +23942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>30</v>
       </c>
@@ -24014,7 +23995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>30</v>
       </c>
@@ -24067,7 +24048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>30</v>
       </c>
@@ -24120,7 +24101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>30</v>
       </c>
@@ -24173,7 +24154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>30</v>
       </c>
@@ -24226,7 +24207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>30</v>
       </c>
@@ -24279,7 +24260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>30</v>
       </c>
@@ -24332,7 +24313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>30</v>
       </c>
@@ -24385,7 +24366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>30</v>
       </c>
@@ -24438,7 +24419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>30</v>
       </c>
@@ -24491,7 +24472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>30</v>
       </c>
@@ -24544,7 +24525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>30</v>
       </c>
@@ -24597,7 +24578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>30</v>
       </c>
@@ -24650,7 +24631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>30</v>
       </c>
@@ -24703,7 +24684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>30</v>
       </c>
@@ -24756,7 +24737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>30</v>
       </c>
@@ -24809,7 +24790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>30</v>
       </c>
@@ -24862,7 +24843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>30</v>
       </c>
@@ -24915,7 +24896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>30</v>
       </c>
@@ -24968,7 +24949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>30</v>
       </c>
@@ -25021,7 +25002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>30</v>
       </c>
@@ -25074,7 +25055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>30</v>
       </c>
@@ -25127,7 +25108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>30</v>
       </c>
@@ -25180,7 +25161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>30</v>
       </c>
@@ -25233,7 +25214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>30</v>
       </c>
@@ -25286,7 +25267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>30</v>
       </c>
@@ -25339,7 +25320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>30</v>
       </c>
@@ -25392,7 +25373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>30</v>
       </c>
@@ -25445,7 +25426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>30</v>
       </c>
@@ -25498,7 +25479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>30</v>
       </c>
@@ -25551,7 +25532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>30</v>
       </c>
@@ -25604,7 +25585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>30</v>
       </c>
@@ -25657,7 +25638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>30</v>
       </c>
@@ -25710,7 +25691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>30</v>
       </c>
@@ -25763,7 +25744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>30</v>
       </c>
@@ -25816,7 +25797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>30</v>
       </c>
@@ -25869,7 +25850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>30</v>
       </c>
@@ -25922,7 +25903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>30</v>
       </c>
@@ -25975,7 +25956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>30</v>
       </c>
@@ -26028,7 +26009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>30</v>
       </c>
@@ -26081,7 +26062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>30</v>
       </c>
@@ -26134,7 +26115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>30</v>
       </c>
@@ -26187,7 +26168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>30</v>
       </c>
@@ -26240,7 +26221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>30</v>
       </c>
@@ -26293,7 +26274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>30</v>
       </c>
@@ -26346,7 +26327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>30</v>
       </c>
@@ -26399,7 +26380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>30</v>
       </c>
@@ -26452,7 +26433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>30</v>
       </c>
@@ -26505,7 +26486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>30</v>
       </c>
@@ -26558,7 +26539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>30</v>
       </c>
@@ -26611,7 +26592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>30</v>
       </c>
@@ -26664,7 +26645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>30</v>
       </c>
@@ -26717,7 +26698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>30</v>
       </c>
@@ -26770,7 +26751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>30</v>
       </c>
@@ -26823,7 +26804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>30</v>
       </c>
@@ -26876,7 +26857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>30</v>
       </c>
@@ -26929,7 +26910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>30</v>
       </c>
@@ -26982,7 +26963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>30</v>
       </c>
@@ -27035,7 +27016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>30</v>
       </c>
@@ -27088,7 +27069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>30</v>
       </c>
@@ -27141,7 +27122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>30</v>
       </c>
@@ -27194,7 +27175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>30</v>
       </c>
@@ -27250,7 +27231,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="353" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
         <v>30</v>
       </c>
@@ -27303,7 +27284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
         <v>30</v>
       </c>
@@ -27356,7 +27337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
         <v>30</v>
       </c>
@@ -27409,7 +27390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
         <v>30</v>
       </c>
@@ -27462,7 +27443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="s">
         <v>30</v>
       </c>
@@ -27515,7 +27496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
         <v>30</v>
       </c>
@@ -27568,7 +27549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
         <v>30</v>
       </c>
@@ -27621,7 +27602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
         <v>30</v>
       </c>
@@ -27674,7 +27655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
         <v>30</v>
       </c>
